--- a/data/metadata/evidence_battery_EV_screened_v0.3.xlsx
+++ b/data/metadata/evidence_battery_EV_screened_v0.3.xlsx
@@ -13,7 +13,7 @@
     <sheet name="screening_rules" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">sources!$A$1:$M$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">sources!$A$1:$M$31</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="812" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="713" uniqueCount="346">
   <si>
     <t>evidence_id</t>
   </si>
@@ -251,7 +251,81 @@
     <t>MOFCOM_002</t>
   </si>
   <si>
-    <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制）</t>
+    <r>
+      <t>商务部公告</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>2025</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体-简"/>
+        <charset val="1"/>
+      </rPr>
+      <t>年第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>72</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体-简"/>
+        <charset val="1"/>
+      </rPr>
+      <t>号（暂停实施</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>2024</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体-简"/>
+        <charset val="1"/>
+      </rPr>
+      <t>年第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>46</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体-简"/>
+        <charset val="1"/>
+      </rPr>
+      <t>号公告第二款，涉及对美两用物项出口管制）</t>
+    </r>
   </si>
   <si>
     <t>商务部</t>
@@ -266,7 +340,7 @@
     <t>待核实原文</t>
   </si>
   <si>
-    <t>data/raw/policy/MOFCOM_002.pdf</t>
+    <t>data/raw/policy/MOFCOM_002.html</t>
   </si>
   <si>
     <t>目前仅见第三方转述：暂停期至2026-11-27，涉及镓、锗、超硬材料、石墨等。入库前须以商务部原文为准。</t>
@@ -275,7 +349,18 @@
     <t>WH_001</t>
   </si>
   <si>
-    <t>Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令）</t>
+    <r>
+      <t>Executive Order 14411: Strengthening Customs Enforcement</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体-简"/>
+        <charset val="1"/>
+      </rPr>
+      <t>（加强海关执法行政令）</t>
+    </r>
   </si>
   <si>
     <t>美国白宫</t>
@@ -302,7 +387,18 @@
     <t>WH_002</t>
   </si>
   <si>
-    <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告）</t>
+    <r>
+      <t>The Great Transshipment Scam: Rise, Scope, and Costs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体-简"/>
+        <charset val="1"/>
+      </rPr>
+      <t>（白宫非法转运报告）</t>
+    </r>
   </si>
   <si>
     <t>官方报告</t>
@@ -314,7 +410,27 @@
     <t>2026-08-13</t>
   </si>
   <si>
-    <t>待补白宫原文链接（已核实来源：https://www.internationaltradeinsights.com/2026/08/white-house-previews-ai-powered-detective-border-tool-targeting-chinese-transshipment/）</t>
+    <r>
+      <t>待补白宫原文链接（已核实来源：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>https://www.internationaltradeinsights.com/2026/08/white-house-previews-ai-powered-detective-border-tool-targeting-chinese-transshipment/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体-简"/>
+        <charset val="1"/>
+      </rPr>
+      <t>）</t>
+    </r>
   </si>
   <si>
     <t>data/raw/policy/WH_002.pdf</t>
@@ -326,7 +442,18 @@
     <t>DOC_001</t>
   </si>
   <si>
-    <t>Final Circumvention Determinations: Crystalline Silicon Photovoltaic Cells from Cambodia, Malaysia, Thailand and Vietnam（东南亚四国光伏反规避终裁）</t>
+    <r>
+      <t>Final Circumvention Determinations: Crystalline Silicon Photovoltaic Cells from Cambodia, Malaysia, Thailand and Vietnam</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体-简"/>
+        <charset val="1"/>
+      </rPr>
+      <t>（东南亚四国光伏反规避终裁）</t>
+    </r>
   </si>
   <si>
     <t>美国商务部</t>
@@ -407,7 +534,54 @@
     <t>WTO_001</t>
   </si>
   <si>
-    <t>Global Trade Outlook and Statistics（2026年3月版）</t>
+    <r>
+      <t>Global Trade Outlook and Statistics</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体-简"/>
+        <charset val="1"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>2026</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体-简"/>
+        <charset val="1"/>
+      </rPr>
+      <t>年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体-简"/>
+        <charset val="1"/>
+      </rPr>
+      <t>月版）</t>
+    </r>
   </si>
   <si>
     <t>世界贸易组织（WTO）</t>
@@ -740,7 +914,45 @@
     <t>TRD_001</t>
   </si>
   <si>
-    <t>美国自中国、越南、泰国、马来西亚进口 HS 851762，2018–2025年度</t>
+    <r>
+      <t>美国自中国、越南、泰国、马来西亚进口</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> HS 870380, 850760</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体-简"/>
+        <charset val="1"/>
+      </rPr>
+      <t>，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>2018–2025</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体-简"/>
+        <charset val="1"/>
+      </rPr>
+      <t>年度</t>
+    </r>
   </si>
   <si>
     <t>贸易数据</t>
@@ -755,7 +967,7 @@
     <t>https://comtradeplus.un.org</t>
   </si>
   <si>
-    <t>◆光模块</t>
+    <t>◆电子/光电</t>
   </si>
   <si>
     <t>待拉取</t>
@@ -770,7 +982,45 @@
     <t>TRD_002</t>
   </si>
   <si>
-    <t>美国自越南、泰国、马来西亚、柬埔寨进口光伏组件，2018–2025年度</t>
+    <r>
+      <t>美国自越南、泰国、马来西亚、柬埔寨进口光伏组件</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>HS 854140</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体-简"/>
+        <charset val="1"/>
+      </rPr>
+      <t>，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>2018–2025</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体-简"/>
+        <charset val="1"/>
+      </rPr>
+      <t>年度</t>
+    </r>
   </si>
   <si>
     <t>◆光伏</t>
@@ -788,63 +1038,12 @@
     <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度</t>
   </si>
   <si>
-    <t>◆电子/光电</t>
-  </si>
-  <si>
     <t>data/raw/trade/TRD_003.csv</t>
   </si>
   <si>
     <t>看东南亚产能是否依赖中国中间品，与原产地风险直接相关。</t>
   </si>
   <si>
-    <t>TRD_004</t>
-  </si>
-  <si>
-    <t>越南、泰国出口中的中国增加值（计算机、电子和光学产品，D26）</t>
-  </si>
-  <si>
-    <t>经合组织（OECD TiVA）</t>
-  </si>
-  <si>
-    <t>越南/泰国</t>
-  </si>
-  <si>
-    <t>持续更新（最新年份滞后数年）</t>
-  </si>
-  <si>
-    <t>https://www.oecd.org/en/topics/sub-issues/trade-in-value-added.html</t>
-  </si>
-  <si>
-    <t>待拉取（链接待核实）</t>
-  </si>
-  <si>
-    <t>data/raw/trade/TRD_004.csv</t>
-  </si>
-  <si>
-    <t>模型估算值而非观测值，报告中须注明。</t>
-  </si>
-  <si>
-    <t>TRD_005</t>
-  </si>
-  <si>
-    <t>美国协调关税表中目标HS编码的当前税率快照（含第99章附加关税）</t>
-  </si>
-  <si>
-    <t>美国国际贸易委员会（USITC）</t>
-  </si>
-  <si>
-    <t>https://hts.usitc.gov</t>
-  </si>
-  <si>
-    <t>关税</t>
-  </si>
-  <si>
-    <t>data/raw/trade/TRD_005.json</t>
-  </si>
-  <si>
-    <t>税率变化快，只存快照并记录抓取日期，产品中实时查询，不写死。</t>
-  </si>
-  <si>
     <t>ITA_001</t>
   </si>
   <si>
@@ -891,63 +1090,6 @@
   </si>
   <si>
     <t>免费，无需key；按机构（BIS/USTR/CBP）过滤。</t>
-  </si>
-  <si>
-    <t>CBP_001</t>
-  </si>
-  <si>
-    <t>CROSS 海关裁定检索系统（原产地与实质性改变裁定）</t>
-  </si>
-  <si>
-    <t>美国海关与边境保护局（CBP）</t>
-  </si>
-  <si>
-    <t>https://rulings.cbp.gov</t>
-  </si>
-  <si>
-    <t>data/raw/database/CBP_001.json</t>
-  </si>
-  <si>
-    <t>无官方API，需检索或爬取；可作原产地判断的标注数据。</t>
-  </si>
-  <si>
-    <t>CNINFO_001</t>
-  </si>
-  <si>
-    <t>巨潮资讯网（上市公司公告）</t>
-  </si>
-  <si>
-    <t>深圳证券信息有限公司</t>
-  </si>
-  <si>
-    <t>https://www.cninfo.com.cn</t>
-  </si>
-  <si>
-    <t>待验证</t>
-  </si>
-  <si>
-    <t>data/raw/database/CNINFO_001.json</t>
-  </si>
-  <si>
-    <t>用于把CASE_004至CASE_008升级为一手证据。</t>
-  </si>
-  <si>
-    <t>MOFCOM_DB_001</t>
-  </si>
-  <si>
-    <t>中国出口管制信息网（两用物项管制清单数据库）</t>
-  </si>
-  <si>
-    <t>待补官网链接</t>
-  </si>
-  <si>
-    <t>待核实链接</t>
-  </si>
-  <si>
-    <t>data/raw/database/MOFCOM_DB_001.json</t>
-  </si>
-  <si>
-    <t>可按编码、名称、管控原因检索。</t>
   </si>
   <si>
     <t>字段</t>
@@ -1191,7 +1333,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1221,9 +1363,10 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <charset val="134"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体-简"/>
+      <charset val="1"/>
     </font>
     <font>
       <u/>
@@ -1240,6 +1383,11 @@
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1686,21 +1834,18 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="42" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
@@ -1709,119 +1854,122 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="5">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="4">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="6">
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1840,6 +1988,18 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="6" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2363,7 +2523,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Y36"/>
+  <dimension ref="A1:Y31"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="25" width="20" customWidth="1"/>
@@ -2472,7 +2632,7 @@
       <c r="I2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="9" t="s">
         <v>33</v>
       </c>
       <c r="K2" s="2" t="s">
@@ -2539,7 +2699,7 @@
       <c r="I3" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="9" t="s">
         <v>47</v>
       </c>
       <c r="K3" s="2" t="s">
@@ -2606,7 +2766,7 @@
       <c r="I4" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" s="9" t="s">
         <v>56</v>
       </c>
       <c r="K4" s="2" t="s">
@@ -2673,7 +2833,7 @@
       <c r="I5" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="J5" s="9" t="s">
         <v>67</v>
       </c>
       <c r="K5" s="2" t="s">
@@ -2718,7 +2878,7 @@
       <c r="A6" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="7" t="s">
         <v>72</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -2785,7 +2945,7 @@
       <c r="A7" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="8" t="s">
         <v>80</v>
       </c>
       <c r="C7" s="2" t="s">
@@ -2852,7 +3012,7 @@
       <c r="A8" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="8" t="s">
         <v>89</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -2874,7 +3034,7 @@
       <c r="I8" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="J8" s="7" t="s">
         <v>93</v>
       </c>
       <c r="K8" s="2" t="s">
@@ -2919,7 +3079,7 @@
       <c r="A9" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="8" t="s">
         <v>97</v>
       </c>
       <c r="C9" s="2" t="s">
@@ -3006,7 +3166,7 @@
       <c r="I10" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="J10" s="2" t="s">
+      <c r="J10" s="9" t="s">
         <v>111</v>
       </c>
       <c r="K10" s="2" t="s">
@@ -3071,7 +3231,7 @@
       <c r="I11" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="J11" s="2" t="s">
+      <c r="J11" s="9" t="s">
         <v>120</v>
       </c>
       <c r="K11" s="2" t="s">
@@ -3116,7 +3276,7 @@
       <c r="A12" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="8" t="s">
         <v>124</v>
       </c>
       <c r="C12" s="2" t="s">
@@ -3203,7 +3363,7 @@
       <c r="I13" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="J13" s="2" t="s">
+      <c r="J13" s="9" t="s">
         <v>137</v>
       </c>
       <c r="K13" s="2" t="s">
@@ -3335,7 +3495,7 @@
       <c r="I15" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="J15" s="2" t="s">
+      <c r="J15" s="9" t="s">
         <v>154</v>
       </c>
       <c r="K15" s="2" t="s">
@@ -3467,7 +3627,7 @@
       <c r="I17" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="J17" s="2" t="s">
+      <c r="J17" s="9" t="s">
         <v>170</v>
       </c>
       <c r="K17" s="2" t="s">
@@ -3532,7 +3692,7 @@
       <c r="I18" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="J18" s="2" t="s">
+      <c r="J18" s="9" t="s">
         <v>182</v>
       </c>
       <c r="K18" s="2" t="s">
@@ -3597,7 +3757,7 @@
       <c r="I19" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="J19" s="2" t="s">
+      <c r="J19" s="9" t="s">
         <v>188</v>
       </c>
       <c r="K19" s="2" t="s">
@@ -3664,7 +3824,7 @@
       <c r="I20" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="J20" s="2" t="s">
+      <c r="J20" s="9" t="s">
         <v>195</v>
       </c>
       <c r="K20" s="2" t="s">
@@ -3731,7 +3891,7 @@
       <c r="I21" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="J21" s="2" t="s">
+      <c r="J21" s="9" t="s">
         <v>195</v>
       </c>
       <c r="K21" s="2" t="s">
@@ -3798,7 +3958,7 @@
       <c r="I22" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="J22" s="2" t="s">
+      <c r="J22" s="9" t="s">
         <v>195</v>
       </c>
       <c r="K22" s="2" t="s">
@@ -3865,7 +4025,7 @@
       <c r="I23" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="J23" s="2" t="s">
+      <c r="J23" s="9" t="s">
         <v>213</v>
       </c>
       <c r="K23" s="2" t="s">
@@ -3932,7 +4092,7 @@
       <c r="I24" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="J24" s="2" t="s">
+      <c r="J24" s="9" t="s">
         <v>220</v>
       </c>
       <c r="K24" s="2" t="s">
@@ -3999,7 +4159,7 @@
       <c r="I25" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="J25" s="2" t="s">
+      <c r="J25" s="9" t="s">
         <v>47</v>
       </c>
       <c r="K25" s="2" t="s">
@@ -4066,7 +4226,7 @@
       <c r="I26" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="J26" s="2" t="s">
+      <c r="J26" s="9" t="s">
         <v>230</v>
       </c>
       <c r="K26" s="2" t="s">
@@ -4111,7 +4271,7 @@
       <c r="A27" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="7" t="s">
         <v>235</v>
       </c>
       <c r="C27" s="2" t="s">
@@ -4133,7 +4293,7 @@
       <c r="I27" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="J27" s="2" t="s">
+      <c r="J27" s="10" t="s">
         <v>239</v>
       </c>
       <c r="K27" s="2" t="s">
@@ -4178,7 +4338,7 @@
       <c r="A28" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="7" t="s">
         <v>245</v>
       </c>
       <c r="C28" s="2" t="s">
@@ -4200,7 +4360,7 @@
       <c r="I28" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="J28" s="2" t="s">
+      <c r="J28" s="9" t="s">
         <v>239</v>
       </c>
       <c r="K28" s="2" t="s">
@@ -4267,7 +4427,7 @@
       <c r="I29" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="J29" s="2" t="s">
+      <c r="J29" s="9" t="s">
         <v>239</v>
       </c>
       <c r="K29" s="2" t="s">
@@ -4280,21 +4440,21 @@
         <v>36</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="O29" s="2" t="s">
         <v>241</v>
       </c>
       <c r="P29" s="2"/>
       <c r="Q29" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="R29" s="2"/>
       <c r="S29" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="T29" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="U29" s="2"/>
       <c r="V29" s="2"/>
@@ -4308,83 +4468,85 @@
         <v>62</v>
       </c>
     </row>
-    <row r="30" ht="31" customHeight="1" spans="1:25">
+    <row r="30" ht="51" spans="1:25">
       <c r="A30" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="B30" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="C30" s="2" t="s">
         <v>255</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>236</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>256</v>
       </c>
       <c r="E30" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G30" s="2" t="s">
         <v>257</v>
-      </c>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2" t="s">
-        <v>258</v>
       </c>
       <c r="H30" s="2"/>
       <c r="I30" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="J30" s="2" t="s">
-        <v>259</v>
+      <c r="J30" s="9" t="s">
+        <v>258</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>112</v>
+        <v>34</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>84</v>
+        <v>35</v>
       </c>
       <c r="M30" s="2" t="s">
         <v>36</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>251</v>
+        <v>37</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>260</v>
+        <v>38</v>
       </c>
       <c r="P30" s="2"/>
       <c r="Q30" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="R30" s="2"/>
       <c r="S30" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="T30" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="U30" s="2"/>
       <c r="V30" s="2"/>
       <c r="W30" s="2" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="X30" s="2" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="Y30" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="31" ht="31" customHeight="1" spans="1:25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="31" ht="51" spans="1:25">
       <c r="A31" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="D31" s="2" t="s">
         <v>263</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>265</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>29</v>
@@ -4393,400 +4555,90 @@
         <v>30</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>238</v>
+        <v>257</v>
       </c>
       <c r="H31" s="2"/>
       <c r="I31" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="J31" s="2" t="s">
-        <v>266</v>
+      <c r="J31" s="9" t="s">
+        <v>264</v>
       </c>
       <c r="K31" s="2" t="s">
         <v>34</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="M31" s="2" t="s">
         <v>36</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>68</v>
+        <v>37</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>241</v>
+        <v>266</v>
       </c>
       <c r="P31" s="2"/>
       <c r="Q31" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="R31" s="2"/>
       <c r="S31" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="T31" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="U31" s="2"/>
       <c r="V31" s="2"/>
       <c r="W31" s="2" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="X31" s="2" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="Y31" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="32" ht="51" spans="1:25">
-      <c r="A32" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="J32" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="K32" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="L32" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="M32" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="N32" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O32" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="P32" s="2"/>
-      <c r="Q32" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="R32" s="2"/>
-      <c r="S32" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="T32" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="U32" s="2"/>
-      <c r="V32" s="2"/>
-      <c r="W32" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="X32" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="Y32" s="2" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="33" ht="51" spans="1:25">
-      <c r="A33" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="J33" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="K33" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="L33" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="M33" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="N33" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O33" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="P33" s="2"/>
-      <c r="Q33" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="R33" s="2"/>
-      <c r="S33" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="T33" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="U33" s="2"/>
-      <c r="V33" s="2"/>
-      <c r="W33" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="X33" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="Y33" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="34" ht="51" spans="1:25">
-      <c r="A34" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="J34" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="K34" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="L34" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="M34" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="N34" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O34" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="P34" s="2"/>
-      <c r="Q34" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="R34" s="2"/>
-      <c r="S34" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="T34" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="U34" s="2"/>
-      <c r="V34" s="2"/>
-      <c r="W34" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="X34" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="Y34" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="35" ht="51" spans="1:25">
-      <c r="A35" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="H35" s="2"/>
-      <c r="I35" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="J35" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="K35" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="L35" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="M35" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="N35" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="O35" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="P35" s="2"/>
-      <c r="Q35" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="R35" s="2"/>
-      <c r="S35" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="T35" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="U35" s="2"/>
-      <c r="V35" s="2"/>
-      <c r="W35" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="X35" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="Y35" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="36" ht="31" customHeight="1" spans="1:25">
-      <c r="A36" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="H36" s="2"/>
-      <c r="I36" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="J36" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="K36" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="L36" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="M36" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="N36" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="O36" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="P36" s="2"/>
-      <c r="Q36" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="R36" s="2"/>
-      <c r="S36" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="T36" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="U36" s="2"/>
-      <c r="V36" s="2"/>
-      <c r="W36" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="X36" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="Y36" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:M36" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:M31" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <dataValidations count="2">
-    <dataValidation type="list" sqref="C2:C235">
+    <dataValidation type="list" sqref="C2:C29 C30:C31 C32:C230">
       <formula1>"法规政策,官方报告,研究报告,调查报告,新闻报道,案例,贸易数据,数据库"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="H2:H235">
+    <dataValidation type="list" sqref="H2:H29 H30:H31 H32:H230">
       <formula1>"S,A+,A,B+,B,C,D"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="J2" r:id="rId1" display="https://www.federalregister.gov/documents/2025/09/30/2025-19001/expansion-of-end-user-controls-to-cover-affiliates-of-certain-listed-entities"/>
+    <hyperlink ref="J3" r:id="rId2" display="https://www.federalregister.gov/documents/2025/11/12/2025-19846/one-year-suspension-of-expansion-of-end-user-controls-for-affiliates-of-certain-listed-entities"/>
+    <hyperlink ref="J4" r:id="rId3" display="https://www.gov.cn/gongbao/2026/issue_12786/202606/content_7071618.html"/>
+    <hyperlink ref="J5" r:id="rId4" display="https://www.mofcom.gov.cn/zwgk/zcfb/art/2025/art_c03d1e511b2b486e829d68e8f1422aff.html"/>
+    <hyperlink ref="J10" r:id="rId5" display="https://www.weforum.org/publications/global-risks-report-2026"/>
+    <hyperlink ref="J11" r:id="rId6" display="https://unctad.org/publication/world-investment-report-2026"/>
+    <hyperlink ref="J13" r:id="rId7" display="https://kpmg.com/us/en/articles/2026/2026-supply-chain-survey.html"/>
+    <hyperlink ref="J15" r:id="rId8" display="https://www.csis.org/analysis/visibility-gap-how-ai-can-stop-chinese-transshipment-under-usmca"/>
+    <hyperlink ref="J17" r:id="rId9" display="https://www.bnnbloomberg.ca/business/international/2026/09/14/companies-left-china-to-dodge-tariffs-now-some-are-heading-back/"/>
+    <hyperlink ref="J18" r:id="rId10" display="https://www.whitecase.com/insight-alert/us-department-commerce-determines-imports-southeast-asia-are-circumventing-addcvd"/>
+    <hyperlink ref="J19" r:id="rId11" display="https://www.internationaltradeinsights.com/2023/08/commerce-issues-final-determination-on-circumvention-of-solar-cells-and-modules-from-cambodia-malaysia-thailand-and-vietnam/"/>
+    <hyperlink ref="J20" r:id="rId12" display="https://news.qq.com/rain/a/20251130A04A7P00"/>
+    <hyperlink ref="J21" r:id="rId12" display="https://news.qq.com/rain/a/20251130A04A7P00"/>
+    <hyperlink ref="J22" r:id="rId12" display="https://news.qq.com/rain/a/20251130A04A7P00"/>
+    <hyperlink ref="J23" r:id="rId13" display="https://www.c114.com.cn/other/241/a1307528.html"/>
+    <hyperlink ref="J24" r:id="rId14" display="https://www.chnfund.com/article/AR9cf00569-dbe0-1615-0b4f-3a13c37ad423"/>
+    <hyperlink ref="J25" r:id="rId2" display="https://www.federalregister.gov/documents/2025/11/12/2025-19846/one-year-suspension-of-expansion-of-end-user-controls-for-affiliates-of-certain-listed-entities"/>
+    <hyperlink ref="J26" r:id="rId15" display="https://www.alvarezandmarsal.com/node/97806"/>
+    <hyperlink ref="J27" r:id="rId16" display="https://comtradeplus.un.org"/>
+    <hyperlink ref="J28" r:id="rId16" display="https://comtradeplus.un.org"/>
+    <hyperlink ref="J29" r:id="rId16" display="https://comtradeplus.un.org"/>
+    <hyperlink ref="J30" r:id="rId17" display="https://www.trade.gov/consolidated-screening-list"/>
+    <hyperlink ref="J31" r:id="rId18" display="https://www.federalregister.gov"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter/>
@@ -4804,35 +4656,35 @@
   <sheetData>
     <row r="1" ht="17" customHeight="1" spans="1:3">
       <c r="A1" s="3" t="s">
-        <v>305</v>
+        <v>269</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>306</v>
+        <v>270</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>307</v>
+        <v>271</v>
       </c>
     </row>
     <row r="2" ht="61" spans="1:3">
       <c r="A2" s="4" t="s">
-        <v>308</v>
+        <v>272</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>309</v>
+        <v>273</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>310</v>
+        <v>274</v>
       </c>
     </row>
     <row r="3" ht="31" spans="1:3">
       <c r="A3" s="5" t="s">
-        <v>311</v>
+        <v>275</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>312</v>
+        <v>276</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>313</v>
+        <v>277</v>
       </c>
     </row>
     <row r="4" ht="61" spans="1:3">
@@ -4840,32 +4692,32 @@
         <v>2</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>314</v>
+        <v>278</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>315</v>
+        <v>279</v>
       </c>
     </row>
     <row r="5" ht="31" spans="1:3">
       <c r="A5" s="5" t="s">
-        <v>316</v>
+        <v>280</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>317</v>
+        <v>281</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>318</v>
+        <v>282</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="5" t="s">
-        <v>319</v>
+        <v>283</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>320</v>
+        <v>284</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>321</v>
+        <v>285</v>
       </c>
     </row>
     <row r="7" ht="46" spans="1:3">
@@ -4873,21 +4725,21 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>322</v>
+        <v>286</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>323</v>
+        <v>287</v>
       </c>
     </row>
     <row r="8" ht="46" spans="1:3">
       <c r="A8" s="5" t="s">
-        <v>324</v>
+        <v>288</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>325</v>
+        <v>289</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>326</v>
+        <v>290</v>
       </c>
     </row>
     <row r="9" ht="31" customHeight="1" spans="1:3">
@@ -4895,21 +4747,21 @@
         <v>10</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>327</v>
+        <v>291</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>328</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10" ht="61" spans="1:3">
       <c r="A10" s="5" t="s">
-        <v>329</v>
+        <v>293</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>330</v>
+        <v>294</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>331</v>
+        <v>295</v>
       </c>
     </row>
     <row r="11" ht="46" spans="1:3">
@@ -4917,43 +4769,43 @@
         <v>16</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>332</v>
+        <v>296</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>333</v>
+        <v>297</v>
       </c>
     </row>
     <row r="12" ht="46" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>334</v>
+        <v>298</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>335</v>
+        <v>299</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>336</v>
+        <v>300</v>
       </c>
     </row>
     <row r="13" ht="61" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>337</v>
+        <v>301</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>338</v>
+        <v>302</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>339</v>
+        <v>303</v>
       </c>
     </row>
     <row r="14" ht="31" spans="1:3">
       <c r="A14" s="5" t="s">
-        <v>340</v>
+        <v>304</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>341</v>
+        <v>305</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>342</v>
+        <v>306</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -4963,87 +4815,87 @@
     </row>
     <row r="16" ht="17" customHeight="1" spans="1:3">
       <c r="A16" s="6" t="s">
-        <v>343</v>
+        <v>307</v>
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="5" t="s">
-        <v>344</v>
+        <v>308</v>
       </c>
       <c r="B17" s="4">
-        <f>COUNTA(sources!A2:A500)</f>
-        <v>35</v>
+        <f>COUNTA(sources!A2:A495)</f>
+        <v>30</v>
       </c>
       <c r="C17" s="4"/>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="5" t="s">
-        <v>345</v>
+        <v>309</v>
       </c>
       <c r="B18" s="4">
-        <f>COUNTIF(sources!C2:C500,"法规政策")+COUNTIF(sources!C2:C500,"官方报告")</f>
+        <f>COUNTIF(sources!C2:C495,"法规政策")+COUNTIF(sources!C2:C495,"官方报告")</f>
         <v>8</v>
       </c>
       <c r="C18" s="4"/>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="5" t="s">
-        <v>346</v>
+        <v>310</v>
       </c>
       <c r="B19" s="4">
-        <f>COUNTIF(sources!C2:C500,"研究报告")+COUNTIF(sources!C2:C500,"调查报告")</f>
+        <f>COUNTIF(sources!C2:C495,"研究报告")+COUNTIF(sources!C2:C495,"调查报告")</f>
         <v>7</v>
       </c>
       <c r="C19" s="4"/>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="5" t="s">
-        <v>347</v>
+        <v>311</v>
       </c>
       <c r="B20" s="4">
-        <f>COUNTIF(sources!A2:A500,"CASE_*")</f>
+        <f>COUNTIF(sources!A2:A495,"CASE_*")</f>
         <v>10</v>
       </c>
       <c r="C20" s="4"/>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="5" t="s">
-        <v>348</v>
+        <v>312</v>
       </c>
       <c r="B21" s="4">
-        <f>COUNTIF(sources!C2:C500,"贸易数据")</f>
-        <v>5</v>
+        <f>COUNTIF(sources!C2:C495,"贸易数据")</f>
+        <v>3</v>
       </c>
       <c r="C21" s="4"/>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="5" t="s">
-        <v>349</v>
+        <v>313</v>
       </c>
       <c r="B22" s="4">
-        <f>COUNTIF(sources!C2:C500,"数据库")</f>
-        <v>5</v>
+        <f>COUNTIF(sources!C2:C495,"数据库")</f>
+        <v>2</v>
       </c>
       <c r="C22" s="4"/>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="4" t="s">
-        <v>350</v>
+        <v>314</v>
       </c>
       <c r="B23" s="4">
-        <f>COUNTIF(sources!H2:H500,"S")</f>
+        <f>COUNTIF(sources!H2:H495,"S")</f>
         <v>0</v>
       </c>
       <c r="C23" s="4"/>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="5" t="s">
-        <v>351</v>
+        <v>315</v>
       </c>
       <c r="B24" s="4">
-        <f>COUNTIF(sources!L2:L500,"待*")</f>
+        <f>COUNTIF(sources!L2:L495,"待*")</f>
         <v>0</v>
       </c>
       <c r="C24" s="4"/>
@@ -5066,13 +4918,13 @@
   <sheetData>
     <row r="1" ht="17" spans="1:3">
       <c r="A1" s="3" t="s">
-        <v>352</v>
+        <v>316</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>353</v>
+        <v>317</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>354</v>
+        <v>318</v>
       </c>
     </row>
     <row r="2" ht="34" spans="1:3">
@@ -5080,10 +4932,10 @@
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>355</v>
+        <v>319</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>356</v>
+        <v>320</v>
       </c>
     </row>
     <row r="3" ht="34" spans="1:3">
@@ -5091,10 +4943,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>357</v>
+        <v>321</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>358</v>
+        <v>322</v>
       </c>
     </row>
     <row r="4" ht="34" spans="1:3">
@@ -5102,10 +4954,10 @@
         <v>5</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>359</v>
+        <v>323</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>360</v>
+        <v>324</v>
       </c>
     </row>
     <row r="5" ht="17" spans="1:3">
@@ -5113,10 +4965,10 @@
         <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>322</v>
+        <v>286</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>361</v>
+        <v>325</v>
       </c>
     </row>
     <row r="6" ht="34" spans="1:3">
@@ -5124,10 +4976,10 @@
         <v>7</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>362</v>
+        <v>326</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>363</v>
+        <v>327</v>
       </c>
     </row>
     <row r="7" ht="51" spans="1:3">
@@ -5135,10 +4987,10 @@
         <v>8</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>364</v>
+        <v>328</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>365</v>
+        <v>329</v>
       </c>
     </row>
     <row r="8" ht="17" spans="1:3">
@@ -5146,10 +4998,10 @@
         <v>10</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>366</v>
+        <v>330</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>367</v>
+        <v>331</v>
       </c>
     </row>
     <row r="9" ht="17" spans="1:3">
@@ -5157,10 +5009,10 @@
         <v>15</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>368</v>
+        <v>332</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>369</v>
+        <v>333</v>
       </c>
     </row>
     <row r="10" ht="17" spans="1:3">
@@ -5168,10 +5020,10 @@
         <v>19</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>370</v>
+        <v>334</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>371</v>
+        <v>335</v>
       </c>
     </row>
     <row r="11" ht="34" spans="1:3">
@@ -5179,10 +5031,10 @@
         <v>20</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>372</v>
+        <v>336</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>373</v>
+        <v>337</v>
       </c>
     </row>
     <row r="12" ht="17" spans="1:3">
@@ -5190,10 +5042,10 @@
         <v>21</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>374</v>
+        <v>338</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>375</v>
+        <v>339</v>
       </c>
     </row>
   </sheetData>
@@ -5213,10 +5065,10 @@
   <sheetData>
     <row r="1" ht="17" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>376</v>
+        <v>340</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>377</v>
+        <v>341</v>
       </c>
     </row>
     <row r="2" ht="68" spans="1:2">
@@ -5224,7 +5076,7 @@
         <v>42</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>378</v>
+        <v>342</v>
       </c>
     </row>
     <row r="3" ht="34" spans="1:2">
@@ -5232,15 +5084,15 @@
         <v>61</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>379</v>
+        <v>343</v>
       </c>
     </row>
     <row r="4" ht="34" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>380</v>
+        <v>344</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>381</v>
+        <v>345</v>
       </c>
     </row>
   </sheetData>
